--- a/Arquivos/nao_atualizaveis/Agendamento_Smart_Factory/Smart Factory Agendamentos.xlsx
+++ b/Arquivos/nao_atualizaveis/Agendamento_Smart_Factory/Smart Factory Agendamentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\FIRJAN\Dashboard\dashboard-firjan\Arquivos\nao_atualizaveis\Agendamento_Smart_Factory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B062E8-D010-4FE4-B9CA-599A04E00C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6490E3E-0B69-466D-AB7A-E29ACC13B8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8E0D1EC4-4AF8-4F28-9F7E-B7A1E945FEC0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="242">
   <si>
     <t>Title</t>
   </si>
@@ -741,6 +741,27 @@
   </si>
   <si>
     <t>NOME DO CONTATO</t>
+  </si>
+  <si>
+    <t>24/07/2026 13:30</t>
+  </si>
+  <si>
+    <t>27/07/2026 13:30</t>
+  </si>
+  <si>
+    <t>20/07/2026 14:30</t>
+  </si>
+  <si>
+    <t>28/07/2026 13:30</t>
+  </si>
+  <si>
+    <t>27/07/2026 10:00</t>
+  </si>
+  <si>
+    <t>20/07/2026 13:30</t>
+  </si>
+  <si>
+    <t>17/07/2026 11:30</t>
   </si>
 </sst>
 </file>
@@ -840,7 +861,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -896,6 +917,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="22" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1443,11 +1467,11 @@
     <col min="3" max="3" width="23.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="60.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.33203125" customWidth="1"/>
+    <col min="7" max="7" width="46.88671875" customWidth="1"/>
     <col min="8" max="8" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="41.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.33203125" customWidth="1"/>
+    <col min="10" max="10" width="41.88671875" customWidth="1"/>
     <col min="11" max="11" width="29.21875" style="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2081,7 +2105,9 @@
       <c r="J19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K19" s="16"/>
+      <c r="K19" s="23" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
@@ -2114,7 +2140,9 @@
       <c r="J20" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="16"/>
+      <c r="K20" s="23" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
@@ -2675,7 +2703,9 @@
       <c r="J37" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K37" s="16"/>
+      <c r="K37" s="16">
+        <v>46227.666666666664</v>
+      </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
@@ -2708,7 +2738,9 @@
       <c r="J38" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K38" s="16"/>
+      <c r="K38" s="16">
+        <v>46225.666666666664</v>
+      </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
@@ -2741,7 +2773,9 @@
       <c r="J39" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K39" s="16"/>
+      <c r="K39" s="16">
+        <v>46220.666666666664</v>
+      </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
@@ -4143,7 +4177,9 @@
       <c r="J81" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K81" s="16"/>
+      <c r="K81" s="23" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
@@ -5343,7 +5379,9 @@
       <c r="J117" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K117" s="16"/>
+      <c r="K117" s="23" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
@@ -5376,7 +5414,9 @@
       <c r="J118" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K118" s="16"/>
+      <c r="K118" s="23" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
@@ -5409,7 +5449,9 @@
       <c r="J119" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="K119" s="16"/>
+      <c r="K119" s="23" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
@@ -5442,7 +5484,9 @@
       <c r="J120" s="9">
         <v>0</v>
       </c>
-      <c r="K120" s="17"/>
+      <c r="K120" s="23" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
@@ -7074,6 +7118,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006E2B4820CFA9404E9EE2CB0E98AA8C81" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="405ac023b8c35b28dd141f5a02842260">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="27b77106-2af4-4f3b-914e-46aa1512cd5d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b2c83184e05df2d4ed63a4b0756c24b7" ns3:_="">
     <xsd:import namespace="27b77106-2af4-4f3b-914e-46aa1512cd5d"/>
@@ -7255,15 +7308,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7273,6 +7317,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE7121F-B6C3-4147-9F67-4EFA37257CA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECC9E2A1-0194-4AFC-8098-A1E7A84EA007}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7290,14 +7342,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE7121F-B6C3-4147-9F67-4EFA37257CA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1959BDFF-9A50-4CA1-A7E7-6C52B5B34A3B}">
   <ds:schemaRefs>
